--- a/research/DCBO/Reports/DCBO_DCF_Model.xlsx
+++ b/research/DCBO/Reports/DCBO_DCF_Model.xlsx
@@ -1013,8 +1013,8 @@
         <v>12</v>
       </c>
       <c r="B10" s="7">
-        <f>B10-B9</f>
-        <v>0</v>
+        <f>B9-B8</f>
+        <v>15.9</v>
       </c>
       <c r="C10" s="2"/>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B27" s="7">
         <f>B11</f>
-        <v>0</v>
+        <v>38.4</v>
       </c>
       <c r="C27" s="7">
-        <f>B27*(1+C21)</f>
-        <v>0</v>
+        <f>B27*(1+B21)</f>
+        <v>46.848</v>
       </c>
       <c r="D27" s="7">
-        <f>C27*(1+D21)</f>
-        <v>0</v>
+        <f>C27*(1+C21)</f>
+        <v>56.2176</v>
       </c>
       <c r="E27" s="7">
-        <f>D27*(1+E21)</f>
-        <v>0</v>
+        <f>D27*(1+D21)</f>
+        <v>65.774592</v>
       </c>
       <c r="F27" s="7">
-        <f>E27*(1+F21)</f>
-        <v>0</v>
+        <f>E27*(1+E21)</f>
+        <v>74.32528896</v>
       </c>
       <c r="G27" s="7">
-        <f>F27*(1+G21)</f>
-        <v>0</v>
+        <f>F27*(1+F21)</f>
+        <v>81.75781786</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1269,23 +1269,23 @@
       </c>
       <c r="C28" s="7">
         <f>1/(1+B16)^1</f>
-        <v>0</v>
+        <v>0.9049773756</v>
       </c>
       <c r="D28" s="7">
         <f>1/(1+B16)^2</f>
-        <v>0</v>
+        <v>0.8189840503</v>
       </c>
       <c r="E28" s="7">
         <f>1/(1+B16)^3</f>
-        <v>0</v>
+        <v>0.7411620365</v>
       </c>
       <c r="F28" s="7">
         <f>1/(1+B16)^4</f>
-        <v>0</v>
+        <v>0.6707348746</v>
       </c>
       <c r="G28" s="7">
         <f>1/(1+B16)^5</f>
-        <v>0</v>
+        <v>0.6069998865</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1294,23 +1294,23 @@
       </c>
       <c r="C29" s="7">
         <f>C27*C28</f>
-        <v>0</v>
+        <v>42.39638009</v>
       </c>
       <c r="D29" s="7">
         <f>D27*D28</f>
-        <v>0</v>
+        <v>46.04131775</v>
       </c>
       <c r="E29" s="7">
         <f>E27*E28</f>
-        <v>0</v>
+        <v>48.74963055</v>
       </c>
       <c r="F29" s="7">
         <f>F27*F28</f>
-        <v>0</v>
+        <v>49.85256337</v>
       </c>
       <c r="G29" s="7">
         <f>G27*G28</f>
-        <v>0</v>
+        <v>49.62698616</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B32" s="7">
         <f>SUM(C29:G29)</f>
-        <v>0</v>
+        <v>236.6668779</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B33" s="7">
         <f>G27*(1+B17)</f>
-        <v>0</v>
+        <v>83.8017633</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B34" s="7">
         <f>B33/(B16-B17)</f>
-        <v>0</v>
+        <v>1047.522041</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B35" s="7">
         <f>B34*G28</f>
-        <v>0</v>
+        <v>635.8457602</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B36" s="7">
         <f>B32+B35</f>
-        <v>0</v>
+        <v>872.5126381</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B37" s="7">
         <f>B10</f>
-        <v>0</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B38" s="7">
         <f>B36-B10</f>
-        <v>0</v>
+        <v>856.6126381</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B39" s="13">
         <f>B38/B7</f>
-        <v>0</v>
+        <v>33.33123106</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B40" s="14">
         <f>B6</f>
-        <v>0</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B41" s="15">
         <f>(B39-B6)/B6</f>
-        <v>0</v>
+        <v>0.902467526</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B44" s="14">
         <f>B34/B7</f>
-        <v>0</v>
+        <v>40.7596125</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B45" s="13">
         <f>B44/(1.15^5)</f>
-        <v>0</v>
+        <v>20.26473108</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B46" s="15">
         <f>(B45-B6)/B6</f>
-        <v>0</v>
+        <v>0.1566627326</v>
       </c>
     </row>
   </sheetData>
@@ -1665,15 +1665,15 @@
       </c>
       <c r="B20" s="7">
         <f>B7*(1+B13)</f>
-        <v>0</v>
+        <v>46.848</v>
       </c>
       <c r="C20" s="7">
         <f>B7*(1+C13)</f>
-        <v>0</v>
+        <v>49.152</v>
       </c>
       <c r="D20" s="7">
         <f>B7*(1+D13)</f>
-        <v>0</v>
+        <v>43.008</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1682,15 +1682,15 @@
       </c>
       <c r="B21" s="7">
         <f>B20*(1+B14)</f>
-        <v>0</v>
+        <v>56.2176</v>
       </c>
       <c r="C21" s="7">
         <f>C20*(1+C14)</f>
-        <v>0</v>
+        <v>61.93152</v>
       </c>
       <c r="D21" s="7">
         <f>D20*(1+D14)</f>
-        <v>0</v>
+        <v>46.87872</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1699,15 +1699,15 @@
       </c>
       <c r="B22" s="7">
         <f>B21*(1+B15)</f>
-        <v>0</v>
+        <v>65.774592</v>
       </c>
       <c r="C22" s="7">
         <f>C21*(1+C15)</f>
-        <v>0</v>
+        <v>75.5564544</v>
       </c>
       <c r="D22" s="7">
         <f>D21*(1+D15)</f>
-        <v>0</v>
+        <v>50.1602304</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1716,15 +1716,15 @@
       </c>
       <c r="B23" s="7">
         <f>B22*(1+B16)</f>
-        <v>0</v>
+        <v>74.32528896</v>
       </c>
       <c r="C23" s="7">
         <f>C22*(1+C16)</f>
-        <v>0</v>
+        <v>89.15661619</v>
       </c>
       <c r="D23" s="7">
         <f>D22*(1+D16)</f>
-        <v>0</v>
+        <v>52.66824192</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1733,15 +1733,15 @@
       </c>
       <c r="B24" s="7">
         <f>B23*(1+B17)</f>
-        <v>0</v>
+        <v>81.75781786</v>
       </c>
       <c r="C24" s="7">
         <f>C23*(1+C17)</f>
-        <v>0</v>
+        <v>101.6385425</v>
       </c>
       <c r="D24" s="7">
         <f>D23*(1+D17)</f>
-        <v>0</v>
+        <v>54.7749716</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1750,15 +1750,15 @@
       </c>
       <c r="B25" s="7">
         <f>B20/(1+B11)^1</f>
-        <v>0</v>
+        <v>42.39638009</v>
       </c>
       <c r="C25" s="7">
         <f>C20/(1+C11)^1</f>
-        <v>0</v>
+        <v>44.88767123</v>
       </c>
       <c r="D25" s="7">
         <f>D20/(1+D11)^1</f>
-        <v>0</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1767,15 +1767,15 @@
       </c>
       <c r="B26" s="7">
         <f>B21/(1+B11)^2</f>
-        <v>0</v>
+        <v>46.04131775</v>
       </c>
       <c r="C26" s="7">
         <f>C21/(1+C11)^2</f>
-        <v>0</v>
+        <v>51.6515669</v>
       </c>
       <c r="D26" s="7">
         <f>D21/(1+D11)^2</f>
-        <v>0</v>
+        <v>37.37142857</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1784,15 +1784,15 @@
       </c>
       <c r="B27" s="7">
         <f>B22/(1+B11)^3</f>
-        <v>0</v>
+        <v>48.74963055</v>
       </c>
       <c r="C27" s="7">
         <f>C22/(1+C11)^3</f>
-        <v>0</v>
+        <v>57.54786449</v>
       </c>
       <c r="D27" s="7">
         <f>D22/(1+D11)^3</f>
-        <v>0</v>
+        <v>35.70306122</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1801,15 +1801,15 @@
       </c>
       <c r="B28" s="7">
         <f>B23/(1+B11)^4</f>
-        <v>0</v>
+        <v>49.85256337</v>
       </c>
       <c r="C28" s="7">
         <f>C23/(1+C11)^4</f>
-        <v>0</v>
+        <v>62.01505032</v>
       </c>
       <c r="D28" s="7">
         <f>D23/(1+D11)^4</f>
-        <v>0</v>
+        <v>33.4716199</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1818,15 +1818,15 @@
       </c>
       <c r="B29" s="7">
         <f>B24/(1+B11)^5</f>
-        <v>0</v>
+        <v>49.62698616</v>
       </c>
       <c r="C29" s="7">
         <f>C24/(1+C11)^5</f>
-        <v>0</v>
+        <v>64.56361403</v>
       </c>
       <c r="D29" s="7">
         <f>D24/(1+D11)^5</f>
-        <v>0</v>
+        <v>31.08078991</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1835,15 +1835,15 @@
       </c>
       <c r="B30" s="7">
         <f>B25+B26+B27+B28+B29</f>
-        <v>0</v>
+        <v>236.6668779</v>
       </c>
       <c r="C30" s="7">
         <f>C25+C26+C27+C28+C29</f>
-        <v>0</v>
+        <v>280.665767</v>
       </c>
       <c r="D30" s="7">
         <f>D25+D26+D27+D28+D29</f>
-        <v>0</v>
+        <v>176.0268996</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1852,15 +1852,15 @@
       </c>
       <c r="B31" s="7">
         <f>B24*(1+B12)/(B11-B12)</f>
-        <v>0</v>
+        <v>1047.522041</v>
       </c>
       <c r="C31" s="7">
         <f>C24*(1+C12)/(C11-C12)</f>
-        <v>0</v>
+        <v>1610.579981</v>
       </c>
       <c r="D31" s="7">
         <f>D24*(1+D12)/(D11-D12)</f>
-        <v>0</v>
+        <v>558.7047103</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1869,15 +1869,15 @@
       </c>
       <c r="B32" s="7">
         <f>B31/(1+B11)^5</f>
-        <v>0</v>
+        <v>635.8457602</v>
       </c>
       <c r="C32" s="7">
         <f>C31/(1+C11)^5</f>
-        <v>0</v>
+        <v>1023.084961</v>
       </c>
       <c r="D32" s="7">
         <f>D31/(1+D11)^5</f>
-        <v>0</v>
+        <v>317.024057</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1886,15 +1886,15 @@
       </c>
       <c r="B33" s="7">
         <f>B30+B32</f>
-        <v>0</v>
+        <v>872.5126381</v>
       </c>
       <c r="C33" s="7">
         <f>C30+C32</f>
-        <v>0</v>
+        <v>1303.750728</v>
       </c>
       <c r="D33" s="7">
         <f>D30+D32</f>
-        <v>0</v>
+        <v>493.0509566</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1903,15 +1903,15 @@
       </c>
       <c r="B34" s="7">
         <f>B33-B6</f>
-        <v>0</v>
+        <v>856.6126381</v>
       </c>
       <c r="C34" s="7">
         <f>C33-B6</f>
-        <v>0</v>
+        <v>1287.850728</v>
       </c>
       <c r="D34" s="7">
         <f>D33-B6</f>
-        <v>0</v>
+        <v>477.1509566</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1920,15 +1920,15 @@
       </c>
       <c r="B35" s="13">
         <f>B34/B5</f>
-        <v>0</v>
+        <v>33.33123106</v>
       </c>
       <c r="C35" s="13">
         <f>C34/B5</f>
-        <v>0</v>
+        <v>50.11092326</v>
       </c>
       <c r="D35" s="13">
         <f>D34/B5</f>
-        <v>0</v>
+        <v>18.56618508</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1937,15 +1937,15 @@
       </c>
       <c r="B36" s="15">
         <f>(B35-B8)/B8</f>
-        <v>0</v>
+        <v>0.902467526</v>
       </c>
       <c r="C36" s="15">
         <f>(C35-B8)/B8</f>
-        <v>0</v>
+        <v>1.860212515</v>
       </c>
       <c r="D36" s="15">
         <f>(D35-B8)/B8</f>
-        <v>0</v>
+        <v>0.05971376044</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B40" s="13">
         <f>B35*B39+C35*C39+D35*D39</f>
-        <v>0</v>
+        <v>32.995908</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B41" s="15">
         <f>(B40-B8)/B8</f>
-        <v>0</v>
+        <v>0.8833280824</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2030,15 +2030,15 @@
       </c>
       <c r="B46" s="7">
         <f>B33/B44</f>
-        <v>0</v>
+        <v>3.207767052</v>
       </c>
       <c r="C46" s="7">
         <f>C33/C44</f>
-        <v>0</v>
+        <v>4.793201205</v>
       </c>
       <c r="D46" s="7">
         <f>D33/D44</f>
-        <v>0</v>
+        <v>1.812687341</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2047,15 +2047,15 @@
       </c>
       <c r="B47" s="7">
         <f>B33/B45</f>
-        <v>0</v>
+        <v>15.72094843</v>
       </c>
       <c r="C47" s="7">
         <f>C33/C45</f>
-        <v>0</v>
+        <v>23.4910041</v>
       </c>
       <c r="D47" s="7">
         <f>D33/D45</f>
-        <v>0</v>
+        <v>8.88380102</v>
       </c>
     </row>
     <row r="48" spans="1:4">
